--- a/XlsxSharp.Tests/Resource/Examples/Misc/DataValidationDecimal.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Misc/DataValidationDecimal.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Sheet1" sheetId="1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -350,92 +350,92 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:B1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:2">
-      <x:c r="A1" s="0">
-        <x:v>1.1</x:v>
-      </x:c>
-      <x:c r="B1" s="0">
-        <x:v>2.1</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:dataValidations count="16">
-    <x:dataValidation type="decimal" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A2:A10">
-      <x:formula1>1.1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="notEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B2:B10">
-      <x:formula1>2.1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C2:C10">
-      <x:formula1>3.1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="lessThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D2:D10">
-      <x:formula1>4.1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E2:E10">
-      <x:formula1>5.1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="lessThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="F2:F10">
-      <x:formula1>6.1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G2:G10">
-      <x:formula1>7.1</x:formula1>
-      <x:formula2>8.1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="notBetween" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="H2:H10">
-      <x:formula1>9.1</x:formula1>
-      <x:formula2>10.1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A11:A20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="notEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B11:B20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C11:C20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="lessThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D11:D20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E11:E20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="lessThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="F11:F20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G11:G20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2>$B$1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="notBetween" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="H11:H20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2>$B$1</x:formula2>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="0">
+        <v>1.1</v>
+      </c>
+      <c r="B1" s="0">
+        <v>2.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="16">
+    <dataValidation type="decimal" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A2:A10">
+      <formula1>1.1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="notEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B2:B10">
+      <formula1>2.1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C2:C10">
+      <formula1>3.1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="lessThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D2:D10">
+      <formula1>4.1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E2:E10">
+      <formula1>5.1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="lessThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="F2:F10">
+      <formula1>6.1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G2:G10">
+      <formula1>7.1</formula1>
+      <formula2>8.1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="notBetween" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="H2:H10">
+      <formula1>9.1</formula1>
+      <formula2>10.1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A11:A20">
+      <formula1>$A$1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="notEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B11:B20">
+      <formula1>$A$1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C11:C20">
+      <formula1>$A$1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="lessThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D11:D20">
+      <formula1>$A$1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E11:E20">
+      <formula1>$A$1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="lessThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="F11:F20">
+      <formula1>$A$1</formula1>
+      <formula2/>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G11:G20">
+      <formula1>$A$1</formula1>
+      <formula2>$B$1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="notBetween" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="H11:H20">
+      <formula1>$A$1</formula1>
+      <formula2>$B$1</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>